--- a/СВО на 13.08.2026.xlsx
+++ b/СВО на 13.08.2026.xlsx
@@ -8,10 +8,10 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="состоят на учете на 15.07.26" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="состоят на учете на 13.08.26" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'состоят на учете на 15.07.26'!$A$1:$AA$27</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'состоят на учете на 13.08.26'!$A$1:$AA$27</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
